--- a/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55929683-5F02-EF48-B469-9CC31982EF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39744E38-C2F8-114E-9A42-43435FDF6DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9380" yWindow="1020" windowWidth="27900" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
+    <workbookView xWindow="-620" yWindow="4820" windowWidth="27900" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>Document ID</t>
   </si>
@@ -58,64 +58,55 @@
     <t>CF_M01</t>
   </si>
   <si>
-    <t>CF_M01_M01</t>
+    <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU10</t>
+  </si>
+  <si>
+    <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+  </si>
+  <si>
+    <t>Gives the ability to handle partial system crashes</t>
+  </si>
+  <si>
+    <t>CF_M01_AU16</t>
+  </si>
+  <si>
+    <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+  </si>
+  <si>
+    <t>CF_M01_P03</t>
+  </si>
+  <si>
+    <t>CF_M01_AD01</t>
+  </si>
+  <si>
+    <t>CF_M01_AD02</t>
   </si>
   <si>
     <t>CF_M01_AD03</t>
   </si>
   <si>
-    <t>CF_M01_C01</t>
-  </si>
-  <si>
-    <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
-  </si>
-  <si>
-    <t>CF_M01_M02</t>
-  </si>
-  <si>
-    <t>CF_M01_C02</t>
-  </si>
-  <si>
-    <t>CF_M01_M03</t>
-  </si>
-  <si>
-    <t>CF_M01_C03</t>
-  </si>
-  <si>
-    <t>CF_M01_M04</t>
-  </si>
-  <si>
-    <t>CF_M01_AU10</t>
-  </si>
-  <si>
-    <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
-  </si>
-  <si>
-    <t>CF_M01_M05</t>
-  </si>
-  <si>
-    <t>CF_M01_C04</t>
-  </si>
-  <si>
-    <t>Gives the ability to handle partial system crashes</t>
-  </si>
-  <si>
-    <t>CF_M01_M06</t>
-  </si>
-  <si>
-    <t>CF_M01_AU16</t>
-  </si>
-  <si>
-    <t>CF_M01_C05</t>
-  </si>
-  <si>
-    <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
-  </si>
-  <si>
-    <t>CF_M01_M07</t>
-  </si>
-  <si>
-    <t>CF_M01_C06</t>
+    <t>CF_M01_AD04</t>
+  </si>
+  <si>
+    <t>CF_M01_AD05</t>
+  </si>
+  <si>
+    <t>CF_M01_C07</t>
+  </si>
+  <si>
+    <t>CF_M01_C07, CF_M01_C08, CF_M01_C02</t>
+  </si>
+  <si>
+    <t>CF_M01_C09</t>
+  </si>
+  <si>
+    <t>CF_M01_C10</t>
+  </si>
+  <si>
+    <t>CF_M01_C11</t>
   </si>
 </sst>
 </file>
@@ -191,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -211,9 +202,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -532,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492A3DD4-FC69-984C-977C-946BA960D4E2}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -566,16 +554,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="4">
         <v>42</v>
@@ -586,39 +574,39 @@
         <v>6</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="F3" s="7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28" x14ac:dyDescent="0.2">
@@ -626,22 +614,22 @@
         <v>6</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="F5" s="7">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -649,55 +637,15 @@
         <v>18</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="7">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="4">
         <v>46</v>
       </c>
     </row>

--- a/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39744E38-C2F8-114E-9A42-43435FDF6DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7D8C3C-51FA-4C42-ADA5-913843F7BD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-620" yWindow="4820" windowWidth="27900" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
+    <workbookView xWindow="680" yWindow="2000" windowWidth="11940" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>Document ID</t>
   </si>
@@ -91,22 +91,16 @@
     <t>CF_M01_AD04</t>
   </si>
   <si>
-    <t>CF_M01_AD05</t>
-  </si>
-  <si>
-    <t>CF_M01_C07</t>
-  </si>
-  <si>
-    <t>CF_M01_C07, CF_M01_C08, CF_M01_C02</t>
-  </si>
-  <si>
-    <t>CF_M01_C09</t>
-  </si>
-  <si>
-    <t>CF_M01_C10</t>
-  </si>
-  <si>
-    <t>CF_M01_C11</t>
+    <t>*CF_M01_C07</t>
+  </si>
+  <si>
+    <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+  </si>
+  <si>
+    <t>*CF_M01_C08</t>
+  </si>
+  <si>
+    <t>*CF_M01_C09, *CF_M01_C10</t>
   </si>
 </sst>
 </file>
@@ -520,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492A3DD4-FC69-984C-977C-946BA960D4E2}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -560,7 +554,7 @@
         <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>7</v>
@@ -580,7 +574,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>9</v>
@@ -600,7 +594,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>10</v>
@@ -620,32 +614,12 @@
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="7">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="4">
         <v>46</v>
       </c>
     </row>

--- a/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7D8C3C-51FA-4C42-ADA5-913843F7BD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447DD7A4-FCB6-F34E-AAAB-3385A980EC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="2000" windowWidth="11940" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
+    <workbookView xWindow="680" yWindow="1480" windowWidth="11940" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Document ID</t>
   </si>
@@ -101,6 +101,36 @@
   </si>
   <si>
     <t>*CF_M01_C09, *CF_M01_C10</t>
+  </si>
+  <si>
+    <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
+  </si>
+  <si>
+    <t>CF_M01_AD05</t>
+  </si>
+  <si>
+    <t>CF_M01_AU34</t>
+  </si>
+  <si>
+    <t>*CF_M01_C11</t>
+  </si>
+  <si>
+    <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU33</t>
+  </si>
+  <si>
+    <t>CF_M01_AD06</t>
+  </si>
+  <si>
+    <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+  </si>
+  <si>
+    <t>CF_M01_C01</t>
+  </si>
+  <si>
+    <t>CF_M01_AD07</t>
   </si>
 </sst>
 </file>
@@ -176,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,6 +229,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492A3DD4-FC69-984C-977C-946BA960D4E2}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -623,6 +656,63 @@
         <v>46</v>
       </c>
     </row>
+    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M01_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447DD7A4-FCB6-F34E-AAAB-3385A980EC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA2AA12-2BCF-3944-BB67-EB29FB87CDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="1480" windowWidth="11940" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
+    <workbookView xWindow="4000" yWindow="1300" windowWidth="22080" windowHeight="16420" xr2:uid="{2B77A409-4A0A-9944-8DFB-55F0A25FF29E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>Document ID</t>
   </si>
@@ -131,6 +131,15 @@
   </si>
   <si>
     <t>CF_M01_AD07</t>
+  </si>
+  <si>
+    <t>This service, being a serverless service, makes it unnecessary to manage the infrastructure when there is an increase in the data set and users.</t>
+  </si>
+  <si>
+    <t>CF_M01_AU20</t>
+  </si>
+  <si>
+    <t>CF_M01_AD08</t>
   </si>
 </sst>
 </file>
@@ -547,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492A3DD4-FC69-984C-977C-946BA960D4E2}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -712,6 +721,29 @@
       <c r="E8" t="s">
         <v>29</v>
       </c>
+      <c r="F8" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="7">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
